--- a/src/main/resources/espacios/Software/PENDIENTE_0 - Spring.xlsx
+++ b/src/main/resources/espacios/Software/PENDIENTE_0 - Spring.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="461">
   <si>
     <t xml:space="preserve">Spring AOP</t>
   </si>
@@ -1435,6 +1435,9 @@
   <si>
     <t xml:space="preserve">42. Spring Cloud Stream Bindings</t>
   </si>
+  <si>
+    <t xml:space="preserve">Spring TX</t>
+  </si>
 </sst>
 </file>
 
@@ -1443,7 +1446,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1466,9 +1469,24 @@
       <family val="0"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="1"/>
     </font>
     <font>
@@ -1533,9 +1551,25 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1546,23 +1580,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1584,14 +1610,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>164160</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>146880</xdr:rowOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>156960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3259080</xdr:colOff>
+      <xdr:colOff>3258360</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>2271960</xdr:rowOff>
+      <xdr:rowOff>2118960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1604,8 +1630,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="23106600" y="7373880"/>
-          <a:ext cx="3094920" cy="2125080"/>
+          <a:off x="23106240" y="7373880"/>
+          <a:ext cx="3094200" cy="2124360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1622,14 +1648,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>10080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3085560</xdr:colOff>
+      <xdr:colOff>3084840</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>1828080</xdr:rowOff>
+      <xdr:rowOff>1675080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1642,8 +1668,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22942440" y="11402640"/>
-          <a:ext cx="3085560" cy="1828080"/>
+          <a:off x="22942080" y="11402640"/>
+          <a:ext cx="3084840" cy="1827360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1660,14 +1686,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>1964160</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3704760</xdr:colOff>
+      <xdr:colOff>3704040</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>818280</xdr:rowOff>
+      <xdr:rowOff>664920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1680,8 +1706,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22942440" y="13519080"/>
-          <a:ext cx="3704760" cy="818280"/>
+          <a:off x="22942080" y="13519080"/>
+          <a:ext cx="3704040" cy="817560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1698,14 +1724,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>150480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3028320</xdr:colOff>
+      <xdr:colOff>3027600</xdr:colOff>
       <xdr:row>81</xdr:row>
-      <xdr:rowOff>1180440</xdr:rowOff>
+      <xdr:rowOff>1027440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1718,8 +1744,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22942440" y="20727720"/>
-          <a:ext cx="3028320" cy="1180440"/>
+          <a:off x="22942080" y="20727720"/>
+          <a:ext cx="3027600" cy="1179720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1736,14 +1762,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>83</xdr:row>
+      <xdr:rowOff>10080</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2790360</xdr:colOff>
+      <xdr:colOff>2789640</xdr:colOff>
       <xdr:row>84</xdr:row>
-      <xdr:rowOff>990000</xdr:rowOff>
+      <xdr:rowOff>836640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1756,8 +1782,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22942440" y="22457880"/>
-          <a:ext cx="2790360" cy="990000"/>
+          <a:off x="22942080" y="22457880"/>
+          <a:ext cx="2789640" cy="989280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1774,14 +1800,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>84</xdr:row>
+      <xdr:rowOff>1173960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2961720</xdr:colOff>
+      <xdr:colOff>2961000</xdr:colOff>
       <xdr:row>85</xdr:row>
-      <xdr:rowOff>1027800</xdr:rowOff>
+      <xdr:rowOff>874440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1794,8 +1820,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22942440" y="23784480"/>
-          <a:ext cx="2961720" cy="1027800"/>
+          <a:off x="22942080" y="23784480"/>
+          <a:ext cx="2961000" cy="1027080"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1812,14 +1838,14 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>150480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2923560</xdr:colOff>
+      <xdr:colOff>2922840</xdr:colOff>
       <xdr:row>88</xdr:row>
-      <xdr:rowOff>1380240</xdr:rowOff>
+      <xdr:rowOff>1226880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1832,8 +1858,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22942440" y="25497720"/>
-          <a:ext cx="2923560" cy="1380240"/>
+          <a:off x="22942080" y="25497720"/>
+          <a:ext cx="2922840" cy="1379520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1860,9 +1886,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3228480</xdr:colOff>
+      <xdr:colOff>3227760</xdr:colOff>
       <xdr:row>61</xdr:row>
-      <xdr:rowOff>241920</xdr:rowOff>
+      <xdr:rowOff>241200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1876,7 +1902,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14989320" y="11454120"/>
-          <a:ext cx="3228480" cy="808920"/>
+          <a:ext cx="3227760" cy="808200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1898,9 +1924,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3114360</xdr:colOff>
+      <xdr:colOff>3113640</xdr:colOff>
       <xdr:row>119</xdr:row>
-      <xdr:rowOff>30240</xdr:rowOff>
+      <xdr:rowOff>29520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1914,7 +1940,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14989320" y="23967360"/>
-          <a:ext cx="3114360" cy="1666080"/>
+          <a:ext cx="3113640" cy="1665360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1936,9 +1962,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3619080</xdr:colOff>
+      <xdr:colOff>3618360</xdr:colOff>
       <xdr:row>129</xdr:row>
-      <xdr:rowOff>104760</xdr:rowOff>
+      <xdr:rowOff>104040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1952,7 +1978,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14989320" y="26040600"/>
-          <a:ext cx="3619080" cy="1713960"/>
+          <a:ext cx="3618360" cy="1713240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1974,9 +2000,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2314080</xdr:colOff>
+      <xdr:colOff>2313360</xdr:colOff>
       <xdr:row>130</xdr:row>
-      <xdr:rowOff>1069560</xdr:rowOff>
+      <xdr:rowOff>1068840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1990,7 +2016,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="14989320" y="28082880"/>
-          <a:ext cx="2314080" cy="799200"/>
+          <a:ext cx="2313360" cy="798480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2017,9 +2043,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2685600</xdr:colOff>
+      <xdr:colOff>2684880</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>902160</xdr:rowOff>
+      <xdr:rowOff>901440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2033,7 +2059,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="1300320"/>
-          <a:ext cx="2685600" cy="1323360"/>
+          <a:ext cx="2684880" cy="1322640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2055,9 +2081,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4142880</xdr:colOff>
+      <xdr:colOff>4142160</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>676440</xdr:rowOff>
+      <xdr:rowOff>675720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2071,7 +2097,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="3608640"/>
-          <a:ext cx="4142880" cy="1237680"/>
+          <a:ext cx="4142160" cy="1236960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2093,9 +2119,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5238720</xdr:colOff>
+      <xdr:colOff>5238000</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>771120</xdr:rowOff>
+      <xdr:rowOff>770400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2109,7 +2135,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="5302800"/>
-          <a:ext cx="5238720" cy="1332720"/>
+          <a:ext cx="5238000" cy="1332000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2131,9 +2157,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3028320</xdr:colOff>
+      <xdr:colOff>3027600</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>195480</xdr:rowOff>
+      <xdr:rowOff>194760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2147,7 +2173,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="9680400"/>
-          <a:ext cx="3028320" cy="1037520"/>
+          <a:ext cx="3027600" cy="1036800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2169,9 +2195,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3971520</xdr:colOff>
+      <xdr:colOff>3970800</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>1029240</xdr:rowOff>
+      <xdr:rowOff>1028520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2185,7 +2211,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="12553920"/>
-          <a:ext cx="3971520" cy="2152080"/>
+          <a:ext cx="3970800" cy="2151360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2207,9 +2233,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3666600</xdr:colOff>
+      <xdr:colOff>3665880</xdr:colOff>
       <xdr:row>113</xdr:row>
-      <xdr:rowOff>104400</xdr:rowOff>
+      <xdr:rowOff>103680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2223,7 +2249,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="28221480"/>
-          <a:ext cx="3666600" cy="2075760"/>
+          <a:ext cx="3665880" cy="2075040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2245,9 +2271,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3257280</xdr:colOff>
+      <xdr:colOff>3256560</xdr:colOff>
       <xdr:row>125</xdr:row>
-      <xdr:rowOff>112680</xdr:rowOff>
+      <xdr:rowOff>111960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2261,7 +2287,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="33207480"/>
-          <a:ext cx="3257280" cy="1551960"/>
+          <a:ext cx="3256560" cy="1551240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2283,9 +2309,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2437920</xdr:colOff>
+      <xdr:colOff>2437200</xdr:colOff>
       <xdr:row>135</xdr:row>
-      <xdr:rowOff>51120</xdr:rowOff>
+      <xdr:rowOff>50400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2299,7 +2325,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="35626680"/>
-          <a:ext cx="2437920" cy="837360"/>
+          <a:ext cx="2437200" cy="836640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2321,9 +2347,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4428720</xdr:colOff>
+      <xdr:colOff>4428000</xdr:colOff>
       <xdr:row>136</xdr:row>
-      <xdr:rowOff>1680120</xdr:rowOff>
+      <xdr:rowOff>1679400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2337,7 +2363,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="37465560"/>
-          <a:ext cx="4428720" cy="789840"/>
+          <a:ext cx="4428000" cy="789120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2359,9 +2385,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3619080</xdr:colOff>
+      <xdr:colOff>3618360</xdr:colOff>
       <xdr:row>141</xdr:row>
-      <xdr:rowOff>747000</xdr:rowOff>
+      <xdr:rowOff>746280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2375,7 +2401,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="39094920"/>
-          <a:ext cx="3619080" cy="646920"/>
+          <a:ext cx="3618360" cy="646200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2397,9 +2423,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2694960</xdr:colOff>
+      <xdr:colOff>2694240</xdr:colOff>
       <xdr:row>147</xdr:row>
-      <xdr:rowOff>576360</xdr:rowOff>
+      <xdr:rowOff>575640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2413,7 +2439,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="40629960"/>
-          <a:ext cx="2694960" cy="780120"/>
+          <a:ext cx="2694240" cy="779400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2435,9 +2461,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3533400</xdr:colOff>
+      <xdr:colOff>3532680</xdr:colOff>
       <xdr:row>153</xdr:row>
-      <xdr:rowOff>82440</xdr:rowOff>
+      <xdr:rowOff>81720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2451,7 +2477,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="42468840"/>
-          <a:ext cx="3533400" cy="961200"/>
+          <a:ext cx="3532680" cy="960480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2473,9 +2499,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2666520</xdr:colOff>
+      <xdr:colOff>2665800</xdr:colOff>
       <xdr:row>161</xdr:row>
-      <xdr:rowOff>55440</xdr:rowOff>
+      <xdr:rowOff>54720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2489,7 +2515,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="44739000"/>
-          <a:ext cx="2666520" cy="828000"/>
+          <a:ext cx="2665800" cy="827280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2511,9 +2537,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2199600</xdr:colOff>
+      <xdr:colOff>2198880</xdr:colOff>
       <xdr:row>165</xdr:row>
-      <xdr:rowOff>161640</xdr:rowOff>
+      <xdr:rowOff>160920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2527,7 +2553,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="46625400"/>
-          <a:ext cx="2199600" cy="970920"/>
+          <a:ext cx="2198880" cy="970200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2549,9 +2575,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2133000</xdr:colOff>
+      <xdr:colOff>2132280</xdr:colOff>
       <xdr:row>171</xdr:row>
-      <xdr:rowOff>1800</xdr:rowOff>
+      <xdr:rowOff>1080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2565,7 +2591,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="48733200"/>
-          <a:ext cx="2133000" cy="589680"/>
+          <a:ext cx="2132280" cy="588960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2587,9 +2613,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2295000</xdr:colOff>
+      <xdr:colOff>2294280</xdr:colOff>
       <xdr:row>177</xdr:row>
-      <xdr:rowOff>122400</xdr:rowOff>
+      <xdr:rowOff>121680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2603,7 +2629,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="51082560"/>
-          <a:ext cx="2295000" cy="608760"/>
+          <a:ext cx="2294280" cy="608040"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2625,9 +2651,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2675880</xdr:colOff>
+      <xdr:colOff>2675160</xdr:colOff>
       <xdr:row>182</xdr:row>
-      <xdr:rowOff>460800</xdr:rowOff>
+      <xdr:rowOff>460080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2641,7 +2667,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="52490880"/>
-          <a:ext cx="2675880" cy="351720"/>
+          <a:ext cx="2675160" cy="351000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2663,9 +2689,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4266720</xdr:colOff>
+      <xdr:colOff>4266000</xdr:colOff>
       <xdr:row>219</xdr:row>
-      <xdr:rowOff>24840</xdr:rowOff>
+      <xdr:rowOff>24120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2679,7 +2705,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="58162320"/>
-          <a:ext cx="4266720" cy="2675880"/>
+          <a:ext cx="4266000" cy="2675160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2701,9 +2727,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4838400</xdr:colOff>
+      <xdr:colOff>4837680</xdr:colOff>
       <xdr:row>226</xdr:row>
-      <xdr:rowOff>1144440</xdr:rowOff>
+      <xdr:rowOff>1143720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2717,7 +2743,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="61567200"/>
-          <a:ext cx="4838400" cy="1809000"/>
+          <a:ext cx="4837680" cy="1808280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2739,9 +2765,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5238720</xdr:colOff>
+      <xdr:colOff>5238000</xdr:colOff>
       <xdr:row>229</xdr:row>
-      <xdr:rowOff>1829520</xdr:rowOff>
+      <xdr:rowOff>1828800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2755,7 +2781,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="64999800"/>
-          <a:ext cx="5238720" cy="2466360"/>
+          <a:ext cx="5238000" cy="2465640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2777,9 +2803,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4905000</xdr:colOff>
+      <xdr:colOff>4904280</xdr:colOff>
       <xdr:row>238</xdr:row>
-      <xdr:rowOff>410760</xdr:rowOff>
+      <xdr:rowOff>410040</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2793,7 +2819,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="68414400"/>
-          <a:ext cx="4905000" cy="1065960"/>
+          <a:ext cx="4904280" cy="1065240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2815,9 +2841,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2990520</xdr:colOff>
+      <xdr:colOff>2989800</xdr:colOff>
       <xdr:row>240</xdr:row>
-      <xdr:rowOff>45360</xdr:rowOff>
+      <xdr:rowOff>44640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2831,7 +2857,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="70544520"/>
-          <a:ext cx="2990520" cy="1637640"/>
+          <a:ext cx="2989800" cy="1636920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2853,9 +2879,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5257800</xdr:colOff>
+      <xdr:colOff>5257080</xdr:colOff>
       <xdr:row>247</xdr:row>
-      <xdr:rowOff>1012320</xdr:rowOff>
+      <xdr:rowOff>1011600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2869,7 +2895,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="73805400"/>
-          <a:ext cx="5257800" cy="1961640"/>
+          <a:ext cx="5257080" cy="1960920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2891,9 +2917,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4886280</xdr:colOff>
+      <xdr:colOff>4885560</xdr:colOff>
       <xdr:row>265</xdr:row>
-      <xdr:rowOff>137520</xdr:rowOff>
+      <xdr:rowOff>136800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2907,7 +2933,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="80730720"/>
-          <a:ext cx="4886280" cy="1418400"/>
+          <a:ext cx="4885560" cy="1417680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2929,9 +2955,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5067000</xdr:colOff>
+      <xdr:colOff>5066280</xdr:colOff>
       <xdr:row>281</xdr:row>
-      <xdr:rowOff>136440</xdr:rowOff>
+      <xdr:rowOff>135720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2945,7 +2971,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="82987560"/>
-          <a:ext cx="5067000" cy="1761480"/>
+          <a:ext cx="5066280" cy="1760760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2967,9 +2993,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2371320</xdr:colOff>
+      <xdr:colOff>2370600</xdr:colOff>
       <xdr:row>285</xdr:row>
-      <xdr:rowOff>120600</xdr:rowOff>
+      <xdr:rowOff>119880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2983,7 +3009,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="86178240"/>
-          <a:ext cx="2371320" cy="951840"/>
+          <a:ext cx="2370600" cy="951120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3005,9 +3031,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4447800</xdr:colOff>
+      <xdr:colOff>4447080</xdr:colOff>
       <xdr:row>288</xdr:row>
-      <xdr:rowOff>1891800</xdr:rowOff>
+      <xdr:rowOff>1891080</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3021,7 +3047,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="87834600"/>
-          <a:ext cx="4447800" cy="1694880"/>
+          <a:ext cx="4447080" cy="1694160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3043,9 +3069,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5038560</xdr:colOff>
+      <xdr:colOff>5037840</xdr:colOff>
       <xdr:row>298</xdr:row>
-      <xdr:rowOff>68040</xdr:rowOff>
+      <xdr:rowOff>67320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3059,7 +3085,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="90720720"/>
-          <a:ext cx="5038560" cy="1647000"/>
+          <a:ext cx="5037840" cy="1646280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3081,9 +3107,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3018960</xdr:colOff>
+      <xdr:colOff>3018240</xdr:colOff>
       <xdr:row>307</xdr:row>
-      <xdr:rowOff>585720</xdr:rowOff>
+      <xdr:rowOff>585000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3097,7 +3123,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="94344480"/>
-          <a:ext cx="3018960" cy="1752120"/>
+          <a:ext cx="3018240" cy="1751400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3119,9 +3145,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4181040</xdr:colOff>
+      <xdr:colOff>4180320</xdr:colOff>
       <xdr:row>311</xdr:row>
-      <xdr:rowOff>373320</xdr:rowOff>
+      <xdr:rowOff>372600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3135,7 +3161,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="97230600"/>
-          <a:ext cx="4181040" cy="1161360"/>
+          <a:ext cx="4180320" cy="1160640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3157,9 +3183,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4076280</xdr:colOff>
+      <xdr:colOff>4075560</xdr:colOff>
       <xdr:row>320</xdr:row>
-      <xdr:rowOff>101880</xdr:rowOff>
+      <xdr:rowOff>101160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3173,7 +3199,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="99024480"/>
-          <a:ext cx="4076280" cy="3076200"/>
+          <a:ext cx="4075560" cy="3075480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3195,9 +3221,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3504960</xdr:colOff>
+      <xdr:colOff>3504240</xdr:colOff>
       <xdr:row>324</xdr:row>
-      <xdr:rowOff>46440</xdr:rowOff>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3211,7 +3237,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="103066200"/>
-          <a:ext cx="3504960" cy="1075680"/>
+          <a:ext cx="3504240" cy="1074960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3233,9 +3259,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5124240</xdr:colOff>
+      <xdr:colOff>5123520</xdr:colOff>
       <xdr:row>324</xdr:row>
-      <xdr:rowOff>2556720</xdr:rowOff>
+      <xdr:rowOff>2556000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3249,7 +3275,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16165800" y="104785920"/>
-          <a:ext cx="5124240" cy="1866240"/>
+          <a:ext cx="5123520" cy="1865520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3276,9 +3302,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3504960</xdr:colOff>
+      <xdr:colOff>3504240</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>2094840</xdr:rowOff>
+      <xdr:rowOff>2094120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3292,7 +3318,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17326440" y="1217880"/>
-          <a:ext cx="3504960" cy="2133000"/>
+          <a:ext cx="3504240" cy="2132280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3314,9 +3340,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4505040</xdr:colOff>
+      <xdr:colOff>4504320</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>875520</xdr:rowOff>
+      <xdr:rowOff>874800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3330,7 +3356,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17326440" y="4546440"/>
-          <a:ext cx="4505040" cy="913680"/>
+          <a:ext cx="4504320" cy="912960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3352,9 +3378,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>3914280</xdr:colOff>
+      <xdr:colOff>3913560</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>2580840</xdr:rowOff>
+      <xdr:rowOff>2580120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3368,7 +3394,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17326440" y="6360840"/>
-          <a:ext cx="3914280" cy="2619000"/>
+          <a:ext cx="3913560" cy="2618280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3390,9 +3416,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>5343480</xdr:colOff>
+      <xdr:colOff>5342760</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>3123720</xdr:rowOff>
+      <xdr:rowOff>3123000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3406,7 +3432,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17326440" y="10431000"/>
-          <a:ext cx="5343480" cy="3180960"/>
+          <a:ext cx="5342760" cy="3180240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3428,9 +3454,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4457520</xdr:colOff>
+      <xdr:colOff>4456800</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>1304640</xdr:rowOff>
+      <xdr:rowOff>1303920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3444,7 +3470,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17326440" y="15742440"/>
-          <a:ext cx="4457520" cy="1361520"/>
+          <a:ext cx="4456800" cy="1360800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3466,9 +3492,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>4152600</xdr:colOff>
+      <xdr:colOff>4151880</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>2780640</xdr:rowOff>
+      <xdr:rowOff>2779920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3482,7 +3508,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="17326440" y="18754560"/>
-          <a:ext cx="4152600" cy="2837880"/>
+          <a:ext cx="4151880" cy="2837160"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3614,7 +3640,9 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="141.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="2" width="115.21"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="8" min="3" style="2" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="61.91"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="10" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3630,18 +3658,18 @@
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="33.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3652,18 +3680,18 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3674,18 +3702,18 @@
       <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="0" t="s">
+      <c r="F7" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3696,29 +3724,29 @@
       <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F8" s="0" t="s">
+      <c r="F8" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="0" t="s">
+      <c r="F9" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F10" s="0" t="s">
+      <c r="F10" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3729,7 +3757,7 @@
       <c r="B11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="F11" s="0" t="s">
+      <c r="F11" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3740,7 +3768,7 @@
       <c r="B12" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="0" t="s">
+      <c r="F12" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3751,18 +3779,18 @@
       <c r="B13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="0" t="s">
+      <c r="F13" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="33.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="0" t="s">
+      <c r="F14" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3773,18 +3801,18 @@
       <c r="B15" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F15" s="0" t="s">
+      <c r="F15" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="0" t="s">
+      <c r="F16" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3795,7 +3823,7 @@
       <c r="B17" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F17" s="0" t="s">
+      <c r="F17" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3806,7 +3834,7 @@
       <c r="B18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="0" t="s">
+      <c r="F18" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3817,7 +3845,7 @@
       <c r="B19" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="F19" s="0" t="s">
+      <c r="F19" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3828,7 +3856,7 @@
       <c r="B20" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F20" s="0" t="s">
+      <c r="F20" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3839,7 +3867,7 @@
       <c r="B21" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="0" t="s">
+      <c r="F21" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3850,18 +3878,18 @@
       <c r="B22" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F22" s="0" t="s">
+      <c r="F22" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="33.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F23" s="0" t="s">
+      <c r="F23" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -3957,7 +3985,7 @@
       </c>
     </row>
     <row r="36" customFormat="false" ht="191.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="1" t="s">
         <v>62</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -4005,12 +4033,12 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="166.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="87.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="3" t="s">
+      <c r="A47" s="1" t="s">
         <v>73</v>
       </c>
     </row>
@@ -4260,7 +4288,7 @@
       </c>
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="5" t="s">
+      <c r="A84" s="4" t="s">
         <v>133</v>
       </c>
     </row>
@@ -4319,482 +4347,482 @@
   <dimension ref="A1:A156"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="131.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="58.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="131.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="58.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="5" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="5" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="5" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="5" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="5" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="5" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="5" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="5" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="5" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="5" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="5" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="5" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="5" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="5" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="5" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="5" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="5" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="5" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="5" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="5" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="5" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="5" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="5" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="5" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="5" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="5" t="s">
         <v>167</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="5" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="5" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="5" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="5" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="5" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="5" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="5" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="5" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="5" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="5" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="5" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="5" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="5" t="s">
         <v>180</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="5" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="5" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="5" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="5" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="5" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="5" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="5" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="5" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="5" t="s">
         <v>189</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="5" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="140.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="5" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="5" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="5" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="5" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="5" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="5" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="5" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="5" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+      <c r="A73" s="5" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+      <c r="A74" s="5" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="5" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="5" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="5" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="5" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
+      <c r="A93" s="5" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
+      <c r="A95" s="5" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
+      <c r="A97" s="5" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
+      <c r="A99" s="5" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
+      <c r="A101" s="5" t="s">
         <v>209</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1" t="s">
+      <c r="A121" s="5" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1" t="s">
+      <c r="A122" s="5" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="1" t="s">
+      <c r="A124" s="5" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="1" t="s">
+      <c r="A125" s="5" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="1" t="s">
+      <c r="A127" s="5" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="1" t="s">
+      <c r="A128" s="5" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="1" t="s">
+      <c r="A130" s="5" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="1" t="s">
+      <c r="A131" s="5" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="148" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="5" t="s">
+      <c r="A133" s="7" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="94.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="5" t="s">
+      <c r="A135" s="7" t="s">
         <v>219</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="1" t="s">
+      <c r="A137" s="5" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="1" t="s">
+      <c r="A138" s="5" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="1" t="s">
+      <c r="A140" s="5" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="1" t="s">
+      <c r="A141" s="5" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="1" t="s">
+      <c r="A143" s="5" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="1" t="s">
+      <c r="A144" s="5" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="1" t="s">
+      <c r="A146" s="5" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="1" t="s">
+      <c r="A147" s="5" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="1" t="s">
+      <c r="A149" s="5" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A150" s="1" t="s">
+      <c r="A150" s="5" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="1" t="s">
+      <c r="A151" s="5" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="1" t="s">
+      <c r="A152" s="5" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="1" t="s">
+      <c r="A153" s="5" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="1" t="s">
+      <c r="A154" s="5" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="1" t="s">
+      <c r="A155" s="5" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="1" t="s">
+      <c r="A156" s="5" t="s">
         <v>235</v>
       </c>
     </row>
@@ -4818,832 +4846,832 @@
   <dimension ref="A1:A334"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="148.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="80.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="148.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="80.69"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>236</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="5" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="5" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="5" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="5" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="130.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="5" t="s">
         <v>242</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="5" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="120.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="140.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="8" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="7" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="7" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="90.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="5" t="s">
         <v>246</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="5" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="5" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="5" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="98.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="5" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="5" t="s">
         <v>251</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="5" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="5" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="5" t="s">
         <v>254</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="5" t="s">
         <v>255</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="184.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="5" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="5" t="s">
         <v>257</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="5" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="5" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="5" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="5" t="s">
         <v>261</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="5" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="5" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="5" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="5" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="5" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="5" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="5" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="5" t="s">
         <v>269</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="5" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="5" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="5" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="5" t="s">
         <v>273</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="5" t="s">
         <v>274</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="5" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="5" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="5" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="5" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="5" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
+      <c r="A92" s="5" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
+      <c r="A93" s="5" t="s">
         <v>281</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
+      <c r="A95" s="5" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
+      <c r="A96" s="5" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
+      <c r="A97" s="5" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
+      <c r="A99" s="5" t="s">
         <v>285</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
+      <c r="A100" s="5" t="s">
         <v>286</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
+      <c r="A101" s="5" t="s">
         <v>287</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="s">
+      <c r="A103" s="5" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="s">
+      <c r="A104" s="5" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
+      <c r="A105" s="5" t="s">
         <v>290</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
+      <c r="A107" s="5" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
+      <c r="A108" s="5" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="s">
+      <c r="A110" s="5" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="s">
+      <c r="A111" s="5" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1" t="s">
+      <c r="A113" s="5" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="s">
+      <c r="A114" s="5" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="s">
+      <c r="A116" s="5" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="s">
+      <c r="A117" s="5" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="s">
+      <c r="A119" s="5" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="187.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="s">
+      <c r="A120" s="5" t="s">
         <v>300</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1" t="s">
+      <c r="A122" s="5" t="s">
         <v>301</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="5" t="s">
+      <c r="A123" s="7" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="1" t="s">
+      <c r="A134" s="5" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="1" t="s">
+      <c r="A135" s="5" t="s">
         <v>304</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="139.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="1" t="s">
+      <c r="A137" s="5" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="1" t="s">
+      <c r="A138" s="5" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="1" t="s">
+      <c r="A140" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="80.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="1" t="s">
+      <c r="A142" s="5" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="1" t="s">
+      <c r="A143" s="5" t="s">
         <v>308</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="1" t="s">
+      <c r="A145" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="77.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="1" t="s">
+      <c r="A148" s="5" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="1" t="s">
+      <c r="A149" s="5" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="1" t="s">
+      <c r="A151" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="69.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="1" t="s">
+      <c r="A153" s="5" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="1" t="s">
+      <c r="A154" s="5" t="s">
         <v>312</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="1" t="s">
+      <c r="A156" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="80.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="1" t="s">
+      <c r="A158" s="5" t="s">
         <v>313</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="1" t="s">
+      <c r="A159" s="5" t="s">
         <v>314</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A161" s="1" t="s">
+      <c r="A161" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="101.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="1" t="s">
+      <c r="A164" s="5" t="s">
         <v>315</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A165" s="1" t="s">
+      <c r="A165" s="5" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A167" s="1" t="s">
+      <c r="A167" s="5" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="84.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="1" t="s">
+      <c r="A171" s="5" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="1" t="s">
+      <c r="A172" s="5" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A174" s="1" t="s">
+      <c r="A174" s="5" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="101.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="1" t="s">
+      <c r="A177" s="5" t="s">
         <v>321</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A178" s="1" t="s">
+      <c r="A178" s="5" t="s">
         <v>322</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A180" s="1" t="s">
+      <c r="A180" s="5" t="s">
         <v>323</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="108.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="1" t="s">
+      <c r="A183" s="5" t="s">
         <v>324</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A184" s="1" t="s">
+      <c r="A184" s="5" t="s">
         <v>325</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A186" s="1" t="s">
+      <c r="A186" s="5" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A187" s="1" t="s">
+      <c r="A187" s="5" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="59.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="1" t="s">
+      <c r="A190" s="5" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="1" t="s">
+      <c r="A191" s="5" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A193" s="1" t="s">
+      <c r="A193" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="49.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="1" t="s">
+      <c r="A195" s="5" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A196" s="1" t="s">
+      <c r="A196" s="5" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A198" s="1" t="s">
+      <c r="A198" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A217" s="1" t="s">
+      <c r="A217" s="5" t="s">
         <v>332</v>
       </c>
     </row>
     <row r="218" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A218" s="1" t="s">
+      <c r="A218" s="5" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A220" s="1" t="s">
+      <c r="A220" s="5" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="1" t="s">
+      <c r="A221" s="5" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A223" s="1" t="s">
+      <c r="A223" s="5" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A224" s="1" t="s">
+      <c r="A224" s="5" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A225" s="1" t="s">
+      <c r="A225" s="5" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A226" s="1" t="s">
+      <c r="A226" s="5" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="242.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A227" s="1" t="s">
+      <c r="A227" s="5" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A228" s="1" t="s">
+      <c r="A228" s="5" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="167.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A230" s="1" t="s">
+      <c r="A230" s="5" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A231" s="1" t="s">
+      <c r="A231" s="5" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A233" s="1" t="s">
+      <c r="A233" s="5" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A234" s="1" t="s">
+      <c r="A234" s="5" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="235" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A235" s="1" t="s">
+      <c r="A235" s="5" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="217.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A239" s="1" t="s">
+      <c r="A239" s="5" t="s">
         <v>347</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A240" s="1" t="s">
+      <c r="A240" s="5" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A242" s="1" t="s">
+      <c r="A242" s="5" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="129.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A244" s="5" t="s">
+      <c r="A244" s="7" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="248" customFormat="false" ht="159.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A248" s="1" t="s">
+      <c r="A248" s="5" t="s">
         <v>351</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A249" s="1" t="s">
+      <c r="A249" s="5" t="s">
         <v>352</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A251" s="1" t="s">
+      <c r="A251" s="5" t="s">
         <v>353</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A252" s="1" t="s">
+      <c r="A252" s="5" t="s">
         <v>354</v>
       </c>
     </row>
     <row r="255" customFormat="false" ht="174.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A255" s="1" t="s">
+      <c r="A255" s="5" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A256" s="1" t="s">
+      <c r="A256" s="5" t="s">
         <v>356</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A258" s="1" t="s">
+      <c r="A258" s="5" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="260" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A260" s="1" t="s">
+      <c r="A260" s="5" t="s">
         <v>358</v>
       </c>
     </row>
     <row r="261" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A261" s="1" t="s">
+      <c r="A261" s="5" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A262" s="1" t="s">
+      <c r="A262" s="5" t="s">
         <v>360</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A263" s="1" t="s">
+      <c r="A263" s="5" t="s">
         <v>361</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A283" s="1" t="s">
+      <c r="A283" s="5" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="285" customFormat="false" ht="139.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A285" s="1" t="s">
+      <c r="A285" s="5" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="286" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A286" s="1" t="s">
+      <c r="A286" s="5" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="161.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A289" s="1" t="s">
+      <c r="A289" s="5" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A290" s="1" t="s">
+      <c r="A290" s="5" t="s">
         <v>366</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A291" s="1" t="s">
+      <c r="A291" s="5" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A292" s="1" t="s">
+      <c r="A292" s="5" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="293" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A293" s="1" t="s">
+      <c r="A293" s="5" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="92" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A297" s="1" t="s">
+      <c r="A297" s="5" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A298" s="1" t="s">
+      <c r="A298" s="5" t="s">
         <v>371</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A301" s="1" t="s">
+      <c r="A301" s="5" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A304" s="1" t="s">
+      <c r="A304" s="5" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="148" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A308" s="1" t="s">
+      <c r="A308" s="5" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A309" s="1" t="s">
+      <c r="A309" s="5" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="73.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A312" s="1" t="s">
+      <c r="A312" s="5" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A313" s="1" t="s">
+      <c r="A313" s="5" t="s">
         <v>377</v>
       </c>
     </row>
     <row r="314" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A314" s="1" t="s">
+      <c r="A314" s="5" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="150.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A315" s="1" t="s">
+      <c r="A315" s="5" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A316" s="1" t="s">
+      <c r="A316" s="5" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="317" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A317" s="1" t="s">
+      <c r="A317" s="5" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="322" customFormat="false" ht="115.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A322" s="1" t="s">
+      <c r="A322" s="5" t="s">
         <v>381</v>
       </c>
     </row>
     <row r="323" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A323" s="1" t="s">
+      <c r="A323" s="5" t="s">
         <v>382</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="279.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A325" s="1" t="s">
+      <c r="A325" s="5" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A326" s="1" t="s">
+      <c r="A326" s="5" t="s">
         <v>384</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="97" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A329" s="1" t="s">
+      <c r="A329" s="5" t="s">
         <v>385</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A330" s="1" t="s">
+      <c r="A330" s="5" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="157.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A333" s="1" t="s">
+      <c r="A333" s="5" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A334" s="1" t="s">
+      <c r="A334" s="5" t="s">
         <v>388</v>
       </c>
     </row>
@@ -5667,201 +5695,201 @@
   <dimension ref="A1:A46"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="2" width="165.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="82.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="165.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="6" width="82.78"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="5" t="s">
         <v>390</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1"/>
+      <c r="A3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="5" t="s">
         <v>391</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1"/>
+      <c r="A5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="5" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="185.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="5" t="s">
         <v>393</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1"/>
+      <c r="A8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="5" t="s">
         <v>394</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="5" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="5" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1"/>
+      <c r="A12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1"/>
+      <c r="A13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="104.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="5" t="s">
         <v>397</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1"/>
+      <c r="A15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="5" t="s">
         <v>398</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1"/>
+      <c r="A17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="221.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="5" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="5" t="s">
         <v>400</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1"/>
+      <c r="A20" s="5"/>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="5" t="s">
         <v>401</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="5" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="5" t="s">
         <v>403</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1"/>
+      <c r="A24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1"/>
+      <c r="A25" s="5"/>
     </row>
     <row r="26" customFormat="false" ht="281.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="5" t="s">
         <v>404</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="124.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="5" t="s">
         <v>405</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1"/>
+      <c r="A28" s="5"/>
     </row>
     <row r="29" customFormat="false" ht="160.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="5" t="s">
         <v>406</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1"/>
+      <c r="A30" s="5"/>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="5" t="s">
         <v>407</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="5" t="s">
         <v>408</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="5" t="s">
         <v>409</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1"/>
+      <c r="A34" s="5"/>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1"/>
+      <c r="A35" s="5"/>
     </row>
     <row r="36" customFormat="false" ht="263.65" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="5" t="s">
         <v>410</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="5" t="s">
         <v>411</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1"/>
+      <c r="A38" s="5"/>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="5" t="s">
         <v>412</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1"/>
+      <c r="A40" s="5"/>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="5" t="s">
         <v>413</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1"/>
+      <c r="A42" s="5"/>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="5" t="s">
         <v>414</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="5" t="s">
         <v>415</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1"/>
+      <c r="A45" s="5"/>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="5" t="s">
         <v>416</v>
       </c>
     </row>
@@ -5882,225 +5910,230 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A44"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="67.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="6" width="67.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="9" t="s">
         <v>417</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="6" t="s">
         <v>418</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="6" t="s">
         <v>419</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="6" t="s">
         <v>420</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="6" t="s">
         <v>421</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="6" t="s">
         <v>422</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="6" t="s">
         <v>423</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="6" t="s">
         <v>424</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="6" t="s">
         <v>425</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="6" t="s">
         <v>426</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="6" t="s">
         <v>427</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="6" t="s">
         <v>428</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="6" t="s">
         <v>429</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="6" t="s">
         <v>430</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="6" t="s">
         <v>431</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="6" t="s">
         <v>432</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="6" t="s">
         <v>433</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="6" t="s">
         <v>434</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="6" t="s">
         <v>435</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="6" t="s">
         <v>436</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="6" t="s">
         <v>437</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="6" t="s">
         <v>438</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="6" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="6" t="s">
         <v>440</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="6" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="6" t="s">
         <v>442</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="6" t="s">
         <v>443</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="6" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="6" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="6" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="6" t="s">
         <v>447</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+      <c r="A33" s="6" t="s">
         <v>448</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="2" t="s">
+      <c r="A34" s="6" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2" t="s">
+      <c r="A35" s="6" t="s">
         <v>450</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+      <c r="A36" s="6" t="s">
         <v>451</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="2" t="s">
+      <c r="A37" s="6" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="2" t="s">
+      <c r="A38" s="6" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="2" t="s">
+      <c r="A39" s="6" t="s">
         <v>454</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
+      <c r="A40" s="6" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
+      <c r="A41" s="6" t="s">
         <v>456</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="2" t="s">
+      <c r="A42" s="6" t="s">
         <v>457</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
+      <c r="A43" s="6" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="2" t="s">
+      <c r="A44" s="6" t="s">
         <v>459</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="6" t="s">
+        <v>460</v>
       </c>
     </row>
   </sheetData>
